--- a/excel/Windows和Mac平台Edge全量快捷键.xlsx
+++ b/excel/Windows和Mac平台Edge全量快捷键.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\Ai\小程序\Excel显示\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E13D99C-4398-41BF-B053-CF093C81177F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30580BC5-6CCE-4F75-839D-B1261707D764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{FE1719C2-E13F-4248-9A1E-AF19344DE301}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{FE1719C2-E13F-4248-9A1E-AF19344DE301}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="339">
   <si>
     <t>Show or hide the favorites bar</t>
   </si>
@@ -1051,6 +1051,9 @@
   </si>
   <si>
     <t>转至上一选项卡</t>
+  </si>
+  <si>
+    <t>说明2</t>
   </si>
 </sst>
 </file>
@@ -1115,6 +1118,38 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{404DC132-870F-4E31-A0AF-FC48CE26707C}" name="表1" displayName="表1" ref="A1:C85" totalsRowShown="0">
+  <autoFilter ref="A1:C85" xr:uid="{404DC132-870F-4E31-A0AF-FC48CE26707C}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{6252A7D8-223E-46B3-BA4F-951522D48587}" name="快捷键"/>
+    <tableColumn id="2" xr3:uid="{290D94DA-358A-4404-8B9E-4D8D192949B2}" name="说明"/>
+    <tableColumn id="3" xr3:uid="{0911B44A-C7A6-48A1-96D2-C4695CA355EC}" name="说明2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{14A85A5E-F3ED-4927-BD0A-4A79645E0618}" name="表2" displayName="表2" ref="A1:C61" totalsRowShown="0">
+  <autoFilter ref="A1:C61" xr:uid="{14A85A5E-F3ED-4927-BD0A-4A79645E0618}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{AA1C6CF5-6786-4589-8BEC-100FDF3D0E4D}" name="快捷键"/>
+    <tableColumn id="2" xr3:uid="{7C9ADF71-0521-4B76-A908-BB78F5BB6EC3}" name="说明"/>
+    <tableColumn id="3" xr3:uid="{77F674DB-2246-4882-900D-9C03BC63EB61}" name="说明2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1422,7 +1457,7 @@
     <col min="3" max="3" width="76" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -1430,10 +1465,10 @@
         <v>231</v>
       </c>
       <c r="C1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>90</v>
       </c>
@@ -1444,7 +1479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -1455,7 +1490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1466,7 +1501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -1477,7 +1512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -1488,7 +1523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>95</v>
       </c>
@@ -1499,7 +1534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -1510,7 +1545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>97</v>
       </c>
@@ -1521,7 +1556,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -1532,7 +1567,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>100</v>
       </c>
@@ -1543,7 +1578,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>101</v>
       </c>
@@ -1554,7 +1589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>102</v>
       </c>
@@ -1565,7 +1600,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>103</v>
       </c>
@@ -1576,7 +1611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>104</v>
       </c>
@@ -1587,7 +1622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>105</v>
       </c>
@@ -1598,7 +1633,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>106</v>
       </c>
@@ -1609,7 +1644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>107</v>
       </c>
@@ -1620,7 +1655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>108</v>
       </c>
@@ -1631,7 +1666,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>109</v>
       </c>
@@ -1642,7 +1677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>110</v>
       </c>
@@ -1653,7 +1688,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>111</v>
       </c>
@@ -1664,7 +1699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>112</v>
       </c>
@@ -1675,7 +1710,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -1686,7 +1721,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1697,7 +1732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>114</v>
       </c>
@@ -1708,7 +1743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>115</v>
       </c>
@@ -1719,7 +1754,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>116</v>
       </c>
@@ -1730,7 +1765,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>117</v>
       </c>
@@ -1741,7 +1776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1752,7 +1787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>118</v>
       </c>
@@ -1763,7 +1798,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>119</v>
       </c>
@@ -1774,7 +1809,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>120</v>
       </c>
@@ -1785,7 +1820,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>121</v>
       </c>
@@ -1796,7 +1831,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>122</v>
       </c>
@@ -1807,7 +1842,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -1818,7 +1853,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>124</v>
       </c>
@@ -1829,7 +1864,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>125</v>
       </c>
@@ -1840,7 +1875,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>126</v>
       </c>
@@ -1851,7 +1886,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>127</v>
       </c>
@@ -1862,7 +1897,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>128</v>
       </c>
@@ -1873,7 +1908,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -1884,7 +1919,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>130</v>
       </c>
@@ -1895,7 +1930,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>131</v>
       </c>
@@ -1906,7 +1941,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -1917,7 +1952,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>133</v>
       </c>
@@ -1928,7 +1963,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>134</v>
       </c>
@@ -1939,7 +1974,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>135</v>
       </c>
@@ -1950,7 +1985,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>136</v>
       </c>
@@ -1961,7 +1996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>137</v>
       </c>
@@ -1972,7 +2007,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -1983,7 +2018,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>139</v>
       </c>
@@ -1994,7 +2029,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>140</v>
       </c>
@@ -2005,7 +2040,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>50</v>
       </c>
@@ -2016,7 +2051,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>142</v>
       </c>
@@ -2027,7 +2062,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>143</v>
       </c>
@@ -2038,7 +2073,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>144</v>
       </c>
@@ -2049,7 +2084,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>145</v>
       </c>
@@ -2060,7 +2095,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>54</v>
       </c>
@@ -2071,7 +2106,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>56</v>
       </c>
@@ -2082,7 +2117,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>58</v>
       </c>
@@ -2093,7 +2128,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>146</v>
       </c>
@@ -2104,7 +2139,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>60</v>
       </c>
@@ -2115,7 +2150,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>147</v>
       </c>
@@ -2126,7 +2161,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -2137,7 +2172,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>148</v>
       </c>
@@ -2148,7 +2183,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>149</v>
       </c>
@@ -2159,7 +2194,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -2170,7 +2205,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -2181,7 +2216,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -2192,7 +2227,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>150</v>
       </c>
@@ -2203,7 +2238,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>152</v>
       </c>
@@ -2214,7 +2249,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -2225,7 +2260,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -2236,7 +2271,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -2247,7 +2282,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -2258,7 +2293,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -2269,7 +2304,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -2280,7 +2315,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>154</v>
       </c>
@@ -2291,7 +2326,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -2302,7 +2337,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>155</v>
       </c>
@@ -2313,7 +2348,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2324,7 +2359,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -2335,7 +2370,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -2346,7 +2381,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>156</v>
       </c>
@@ -2360,6 +2395,9 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2373,7 +2411,7 @@
     <col min="3" max="3" width="58.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>230</v>
       </c>
@@ -2381,10 +2419,10 @@
         <v>231</v>
       </c>
       <c r="C1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>232</v>
       </c>
@@ -2395,7 +2433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>233</v>
       </c>
@@ -2406,7 +2444,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>235</v>
       </c>
@@ -2417,7 +2455,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>237</v>
       </c>
@@ -2428,7 +2466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>238</v>
       </c>
@@ -2439,7 +2477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>239</v>
       </c>
@@ -2450,7 +2488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>240</v>
       </c>
@@ -2461,7 +2499,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>242</v>
       </c>
@@ -2472,7 +2510,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>244</v>
       </c>
@@ -2483,7 +2521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>245</v>
       </c>
@@ -2494,7 +2532,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>246</v>
       </c>
@@ -2505,7 +2543,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>247</v>
       </c>
@@ -2516,7 +2554,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>249</v>
       </c>
@@ -2527,7 +2565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>250</v>
       </c>
@@ -2538,7 +2576,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -2549,7 +2587,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>252</v>
       </c>
@@ -2560,7 +2598,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>254</v>
       </c>
@@ -2571,7 +2609,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>256</v>
       </c>
@@ -2582,7 +2620,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>258</v>
       </c>
@@ -2593,7 +2631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>259</v>
       </c>
@@ -2604,7 +2642,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>261</v>
       </c>
@@ -2615,7 +2653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>262</v>
       </c>
@@ -2626,7 +2664,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>264</v>
       </c>
@@ -2637,7 +2675,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>266</v>
       </c>
@@ -2648,7 +2686,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>267</v>
       </c>
@@ -2659,7 +2697,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>268</v>
       </c>
@@ -2670,7 +2708,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>270</v>
       </c>
@@ -2681,7 +2719,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>272</v>
       </c>
@@ -2692,7 +2730,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>273</v>
       </c>
@@ -2703,7 +2741,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>274</v>
       </c>
@@ -2714,7 +2752,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>276</v>
       </c>
@@ -2725,7 +2763,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>277</v>
       </c>
@@ -2736,7 +2774,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>278</v>
       </c>
@@ -2747,7 +2785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>279</v>
       </c>
@@ -2758,7 +2796,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>281</v>
       </c>
@@ -2769,7 +2807,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>282</v>
       </c>
@@ -2780,7 +2818,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>283</v>
       </c>
@@ -2791,7 +2829,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>285</v>
       </c>
@@ -2802,7 +2840,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>287</v>
       </c>
@@ -2813,7 +2851,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>289</v>
       </c>
@@ -2824,7 +2862,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>291</v>
       </c>
@@ -2835,7 +2873,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>292</v>
       </c>
@@ -2846,7 +2884,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>293</v>
       </c>
@@ -2857,7 +2895,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>294</v>
       </c>
@@ -2868,7 +2906,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>295</v>
       </c>
@@ -2879,7 +2917,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>296</v>
       </c>
@@ -2890,7 +2928,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>297</v>
       </c>
@@ -2901,7 +2939,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>299</v>
       </c>
@@ -2912,7 +2950,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>301</v>
       </c>
@@ -2923,7 +2961,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>302</v>
       </c>
@@ -2934,7 +2972,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -2945,7 +2983,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -2956,7 +2994,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>304</v>
       </c>
@@ -2967,7 +3005,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>306</v>
       </c>
@@ -2978,7 +3016,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>307</v>
       </c>
@@ -2989,7 +3027,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>153</v>
       </c>
@@ -3000,7 +3038,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -3011,7 +3049,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>156</v>
       </c>
@@ -3022,7 +3060,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>310</v>
       </c>
@@ -3033,7 +3071,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>312</v>
       </c>
@@ -3047,5 +3085,8 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>